--- a/business_surveys/048_leadership_maturity_assessment_survey--business_surveys.xlsx
+++ b/business_surveys/048_leadership_maturity_assessment_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'ceo/owner'}</t>
+          <t>ceo/owner</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'CEO/Owner'}</t>
+          <t>CEO/Owner</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'employee'}</t>
+          <t>employee</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Employee'}</t>
+          <t>Employee</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'autocratic'}</t>
+          <t>autocratic</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Autocratic'}</t>
+          <t>Autocratic</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'democratic'}</t>
+          <t>democratic</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Democratic'}</t>
+          <t>Democratic</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'laissez-faire'}</t>
+          <t>laissez-faire</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Laissez-faire'}</t>
+          <t>Laissez-faire</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'data-driven'}</t>
+          <t>data-driven</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Data-driven'}</t>
+          <t>Data-driven</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'intuitive'}</t>
+          <t>intuitive</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Intuitive'}</t>
+          <t>Intuitive</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'holistic'}</t>
+          <t>holistic</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Holistic'}</t>
+          <t>Holistic</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'avoids_conflict'}</t>
+          <t>avoids_conflict</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'Avoids conflict'}</t>
+          <t>Avoids conflict</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'manages_conflict'}</t>
+          <t>manages_conflict</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'Manages conflict'}</t>
+          <t>Manages conflict</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'escalates_conflict'}</t>
+          <t>escalates_conflict</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'Escalates conflict'}</t>
+          <t>Escalates conflict</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_'goal-oriented'}</t>
+          <t>goal-oriented</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': 'Goal-oriented'}</t>
+          <t>Goal-oriented</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'value':_'results-oriented'}</t>
+          <t>results-oriented</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'value': 'Results-oriented'}</t>
+          <t>Results-oriented</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'value':_'relationship-oriented'}</t>
+          <t>relationship-oriented</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'value': 'Relationship-oriented'}</t>
+          <t>Relationship-oriented</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'value':_'quantitative_metrics'}</t>
+          <t>quantitative_metrics</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'value': 'Quantitative metrics'}</t>
+          <t>Quantitative metrics</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'value':_'qualitative_feedback'}</t>
+          <t>qualitative_feedback</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'value': 'Qualitative feedback'}</t>
+          <t>Qualitative feedback</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'value':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'value': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'value':_'empowering'}</t>
+          <t>empowering</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'value': 'Empowering'}</t>
+          <t>Empowering</t>
         </is>
       </c>
     </row>
@@ -1896,12 +1896,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'value':_'directing'}</t>
+          <t>directing</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'value': 'Directing'}</t>
+          <t>Directing</t>
         </is>
       </c>
     </row>
@@ -1913,12 +1913,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'value':_'micromanaging'}</t>
+          <t>micromanaging</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'value': 'Micromanaging'}</t>
+          <t>Micromanaging</t>
         </is>
       </c>
     </row>
@@ -1998,12 +1998,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'value':_'solicits_feedback'}</t>
+          <t>solicits_feedback</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'value': 'Solicits feedback'}</t>
+          <t>Solicits feedback</t>
         </is>
       </c>
     </row>
@@ -2015,12 +2015,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'value':_'gives_feedback'}</t>
+          <t>gives_feedback</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'value': 'Gives feedback'}</t>
+          <t>Gives feedback</t>
         </is>
       </c>
     </row>
@@ -2032,12 +2032,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'value':_"doesn't_give_feedback"}</t>
+          <t>doesn't_give_feedback</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'value': "Doesn't give feedback"}</t>
+          <t>Doesn't give feedback</t>
         </is>
       </c>
     </row>
